--- a/DownloadTodosResultadosLoterias/downloads/SUPER_SETE.xlsx
+++ b/DownloadTodosResultadosLoterias/downloads/SUPER_SETE.xlsx
@@ -59929,6 +59929,7406 @@
         <x:v/>
       </x:c>
     </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>803</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>26/01/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$11.588,95</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$704,49</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>455</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$72,77</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4353</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.258.417,19</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$563.736,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.400.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>804</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>28/01/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$7.289,83</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$946,73</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>417</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$74,92</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3959</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.338.605,71</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$529.881,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.450.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>805</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>30/01/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$26.790,41</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.159,75</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>656</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$58,34</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4580</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.436.838,11</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$645.414,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.550.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>806</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>02/02/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$27.656,12</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.362,37</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$71,31</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4899</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.538.246,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$668.613,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.650.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>807</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>04/02/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$8.530,06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$937,36</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$71,40</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4799</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.632.077,34</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$622.311,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.750.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>808</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>06/02/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$9.924,84</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.215,28</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$62,64</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5940</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.741.252,43</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$728.949,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.850.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>809</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>09/02/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.545,94</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$83,24</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4848</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.882.656,18</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$725.427,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>810</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>11/02/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$13.886,74</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.417,01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>495</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$80,15</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5058</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.984.493,87</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$673.344,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.100.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>811</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>13/02/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$29.942,61</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$891,14</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>626</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$68,33</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5447</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.094.284,15</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$725.850,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.200.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>812</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>18/02/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$864,71</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>738</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$60,92</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6300</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.241.174,36</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$770.877,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.400.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>813</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>20/02/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$30.344,91</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.083,74</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>664</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$65,28</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5908</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.352.441,97</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$740.916,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.450.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>814</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>23/02/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.165,89</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>701</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$63,20</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6038</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.497.168,41</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$757.221,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.600.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>815</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>25/02/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$14.427,22</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$352,31</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>557</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$74,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5258</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.602.970,13</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$699.594,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.700.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>816</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>27/02/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$987,39</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>614</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$73,97</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5563</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.751.344,18</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$767.706,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.900.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>817</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>02/03/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.413,40</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>627</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$74,38</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5770</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.903.713,40</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$789.150,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.100.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>818</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>04/03/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$829,83</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>592</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$70,08</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5460</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.039.256,88</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$706.491,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.200.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>819</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>06/03/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$17.103,66</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$708,22</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>686</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$71,23</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5709</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.164.686,61</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$822.192,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.300.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>820</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>09/03/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$11.449,22</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.141,11</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>658</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$74,57</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6267</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.290.628,99</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$832.890,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.500.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>821</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>11/03/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$9.923,56</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.012,60</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>595</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$71,47</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5557</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.399.791,85</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$723.618,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.600.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>822</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>13/03/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.491,57</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>593</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$83,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5751</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.560.585,57</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$828.162,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.700.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>823</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>16/03/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.054,94</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>694</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$69,92</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6081</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.719.110,85</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$822.111,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.800.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>824</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>18/03/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$910,69</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>722</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$64,32</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6054</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.870.836,35</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$790.041,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.900.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>825</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>20/03/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$33.041,08</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$925,52</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>718</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$65,74</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6165</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.991.987,17</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$803.076,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>826</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>23/03/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24.009,21</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.805,20</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>872</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$78,66</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8570</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.168.059,12</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.161.768,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.200.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>827</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>25/03/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$14.655,92</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.046,85</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1091</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$57,57</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9116</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.329.275,79</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.081.152,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.400.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>828</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>27/03/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.219,74</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>990</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$67,76</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9084</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.548.425,25</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.145.793,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.700.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>829</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>30/03/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$15.862,07</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.172,07</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>997</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$68,18</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9979</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.722.911,60</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.171.674,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>830</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>01/04/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$16.414,63</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.192,34</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>981</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$71,71</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8855</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.903.473,50</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.192.326,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.200.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>831</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>06/04/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$19.836,03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.197,34</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1187</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$71,61</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10917</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.121.677,47</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.443.813,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.400.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>832</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>08/04/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$36.358,54</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$895,53</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>870</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$59,70</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7730</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.254.993,38</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$896.670,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.500.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>833</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>10/04/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$18.410,97</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$974,12</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1100</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$71,73</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10015</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.457.515,21</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.338.474,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.700.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>834</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>13/04/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$17.551,83</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.139,72</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1055</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$71,30</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9233</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.650.586,15</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.271.703,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>835</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>15/04/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$7.087,42</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$701,72</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1333</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$53,16</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>11171</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.832.505,41</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.232.064,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.100.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>836</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>17/04/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$17.495,89</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.119,13</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1056</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$71,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10239</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.024.965,06</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.281.837,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.300.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>837</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>20/04/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.106,58</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1187</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$68,05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10852</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.288.851,11</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.378.506,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.500.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>838</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>22/04/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$15.638,30</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$930,85</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1039</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$64,50</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8690</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.460.876,50</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.139.412,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.700.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>839</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>24/04/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$31.694,60</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.437,39</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1194</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$75,84</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>11214</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.693.306,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.532.292,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$7.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>840</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>27/04/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$14.086,86</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$882,63</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1452</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$69,29</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>13583</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.951.573,46</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.717.974,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$7.200.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>841</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>29/04/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>BRASILIA/DF</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$7.176.787,87</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$15.355,42</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.044,58</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1357</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$64,66</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12964</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.513.479,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$100.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>842</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>04/05/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$10.987,76</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.846,68</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$73,34</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3838</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$80.579,79</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$530.529,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$200.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>843</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>06/05/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.289,44</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$79,48</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2824</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$156.400,19</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$392.046,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$250.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>844</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>08/05/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$8.883,84</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.015,29</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$77,38</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2962</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$221.549,77</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$427.011,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$300.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>845</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>11/05/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.199,19</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$70,16</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3053</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$307.733,75</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$443.481,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$400.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>846</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>13/05/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$17.327,11</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$825,10</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>435</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$56,90</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3565</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$371.267,55</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$425.691,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$450.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>847</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>15/05/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$18.890,32</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$899,53</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$79,84</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3310</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$440.532,42</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$456.195,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$500.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>848</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>18/05/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$9.539,37</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$825,91</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>490</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$55,62</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3927</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$510.489,12</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$468.747,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$550.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>849</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>20/05/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.318,83</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>443</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$56,56</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3421</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$592.345,79</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$428.358,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$650.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>850</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>22/05/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$968,16</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>438</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$61,89</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4010</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$680.900,83</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$467.649,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$750.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>851</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>25/05/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$21.772,93</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$942,55</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>424</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$73,35</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3908</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$760.737,56</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$527.082,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$850.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>852</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>27/05/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$19.088,69</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.185,63</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>387</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$70,46</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3264</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$830.730,52</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$459.879,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$900.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>853</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>29/05/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$21.790,82</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.482,36</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$77,43</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3912</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$910.632,35</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$527.526,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>854</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>01/06/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.385,93</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$80,95</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4142</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.023.818,79</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$584.247,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.100.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>855</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>03/06/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$938,81</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>534</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$61,53</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4339</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.131.157,54</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$559.695,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.200.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>856</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>05/06/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$11.518,64</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$645,30</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$77,98</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3980</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.215.629,70</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$555.567,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.300.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>857</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>08/06/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$26.840,20</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$852,06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>570</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$67,26</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5257</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.314.047,56</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$655.773,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.400.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>858</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>10/06/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$25.746,49</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.268,29</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>585</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$62,87</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4975</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.408.452,76</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$628.122,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.500.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>859</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>12/06/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$26.922,08</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.098,86</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>550</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$69,92</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4981</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.507.169,94</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$653.772,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.600.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>860</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>15/06/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$870,74</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>729</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$59,72</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6802</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.649.393,64</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$756.021,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.800.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>861</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>17/06/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$13.795,93</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.126,19</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>537</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$73,40</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5054</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.750.564,76</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$669.339,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.900.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>862</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>20/06/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.873,73</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$835,71</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>652</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$60,24</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5242</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.851.380,99</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$669.807,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>863</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>22/06/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.145,49</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>563</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$77,31</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5435</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.993.576,82</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$737.157,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.100.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>864</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>25/06/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.511,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>489</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$71,06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4319</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.107.106,64</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$588.264,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.200.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>865</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>26/06/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$14.956,02</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.335,35</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>566</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$75,49</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5101</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.216.787,14</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$720.444,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.400.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>866</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>29/06/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$15.744,13</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.451,07</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>676</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$66,54</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6208</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.332.245,63</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$769.893,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.500.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>867</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>01/07/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$30.708,59</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.193,47</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$83,88</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5424</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.444.843,92</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$742.194,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.600.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>868</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>03/07/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$16.881,29</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.339,78</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>597</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$80,79</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6097</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.568.640,62</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$817.836,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.700.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>869</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>06/07/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.123,95</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>708</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$66,67</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6105</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.722.850,83</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$802.326,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.800.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>870</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>08/07/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$7.832,23</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.177,77</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>628</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$71,26</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5572</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.837.726,72</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$757.713,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>871</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>10/07/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$781,11</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>723</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$69,14</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6406</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.001.034,94</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$848.853,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.100.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>872</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>13/07/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$25.074,20</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.705,72</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>887</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$80,76</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8546</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.184.917,19</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.207.764,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.300.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>873</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>15/07/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$17.951,25</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.192,77</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>716</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$71,63</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6482</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.316.561,39</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$869.652,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.500.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>874</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>17/07/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$37.884,89</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.288,60</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>676</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$80,06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6601</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.455.473,19</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$914.397,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.600.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>875</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>20/07/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.244,36</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.029,29</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>895</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$59,80</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6868</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.592.850,72</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$908.949,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.800.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>876</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>22/07/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$34.070,91</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$973,45</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>738</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$65,95</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6673</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.717.778,68</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$832.434,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.900.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>877</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>24/07/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.169,99</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>938</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$59,87</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7773</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.901.235,61</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$961.491,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.100.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>878</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>27/07/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12.374,63</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.433,35</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>739</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$71,76</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7107</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.037.359,04</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$904.779,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.200.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>879</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>29/07/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$11.277,05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$611,77</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>876</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$55,17</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6959</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.161.407,72</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$831.138,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.300.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>880</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>31/07/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$10.330,37</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.513,60</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>880</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$67,08</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7754</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.312.920,22</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.004.937,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.500.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>881</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>03/08/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$906,52</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1062</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$61,45</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9266</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.526.143,48</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.120.644,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.700.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>882</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>05/08/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$20.811,38</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.081,11</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>823</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$72,24</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7699</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.678.765,63</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.010.736,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.900.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>883</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>07/08/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$51.137,77</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.461,07</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>892</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$81,89</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8353</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.866.276,73</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.226.637,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>884</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>10/08/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$25.791,73</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.052,72</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1064</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$69,25</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9303</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.055.422,34</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.249.347,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.200.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>885</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>12/08/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$23.033,80</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.044,61</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>929</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$70,84</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8765</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.224.337,54</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.122.012,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.400.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>886</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>14/08/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$16.219,52</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$772,35</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1248</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$55,69</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10434</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.402.760,40</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.201.230,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.600.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>887</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>17/08/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24.618,43</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.153,08</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1107</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$63,53</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9837</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.583.303,38</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.205.628,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.800.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>888</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>19/08/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$21.620,39</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$791,95</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1171</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$52,75</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9788</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.741.854,86</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.074.549,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>889</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>21/08/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24.055,22</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$996,07</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1015</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$67,71</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9363</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.918.262,56</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.174.635,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.200.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>890</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>24/08/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24.812,27</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.476,92</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>975</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$72,70</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8715</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.100.225,98</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.198.686,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.300.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>891</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>26/08/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$17.398,53</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.021,43</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1097</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$67,97</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10520</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.291.611,74</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.279.335,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.500.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>892</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>28/08/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$11.349,39</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$628,42</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1486</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$54,55</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>11760</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.499.688,55</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.395.312,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.700.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>893</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>31/08/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$55.949,64</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.211,03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1031</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$77,52</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10008</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.704.840,74</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.353.966,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$7.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>894</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>02/09/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$28.008,29</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.231,13</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1138</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$70,31</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9951</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.910.242,71</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.354.641,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$7.200.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>895</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>04/09/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$31.882,86</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.214,58</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1340</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$67,98</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12112</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$7.144.051,09</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.552.785,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$7.500.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>896</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>09/09/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$66.781,46</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.109,32</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1354</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$70,45</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>11585</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$7.388.925,78</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.611.153,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$7.700.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>897</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>11/09/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$30.144,57</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$828,14</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1376</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$62,59</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12177</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$7.609.988,93</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.478.064,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$8.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>898</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>14/09/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$19.865,39</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.182,46</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1085</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$78,46</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10583</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$7.828.514,15</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.441.152,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$8.100.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>899</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>16/09/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$58.913,14</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.335,89</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1253</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$67,16</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10600</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$8.044.536,46</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.426.530,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$8.300.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>18/09/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$25.330,59</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.428,41</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1327</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$81,80</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12759</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$8.323.180,99</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.827.552,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$8.500.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>901</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>21/09/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$9.379,53</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$992,54</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1531</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$70,01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>14438</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$8.598.320,39</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.829.775,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$8.800.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>902</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>23/09/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$36.821,40</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.195,50</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1582</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$66,50</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12789</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$8.868.344,69</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.776.876,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$9.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:phoneticPr fontId="2" type="noConversion"/>
   <x:pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -60117,7 +67517,7 @@
   <documentManagement>
     <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
     <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-01-25T04:12:51+00:00</AtualizadoPeloTimerJobEm>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-09-24T04:13:23+00:00</AtualizadoPeloTimerJobEm>
   </documentManagement>
 </p:properties>
 </file>

--- a/DownloadTodosResultadosLoterias/downloads/SUPER_SETE.xlsx
+++ b/DownloadTodosResultadosLoterias/downloads/SUPER_SETE.xlsx
@@ -67517,7 +67517,7 @@
   <documentManagement>
     <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
     <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-09-24T04:13:23+00:00</AtualizadoPeloTimerJobEm>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-09-25T04:11:17+00:00</AtualizadoPeloTimerJobEm>
   </documentManagement>
 </p:properties>
 </file>

--- a/DownloadTodosResultadosLoterias/downloads/SUPER_SETE.xlsx
+++ b/DownloadTodosResultadosLoterias/downloads/SUPER_SETE.xlsx
@@ -67329,6 +67329,80 @@
         <x:v/>
       </x:c>
     </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>903</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>25/09/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$68.192,86</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.248,95</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1367</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$71,26</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12193</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$9.118.389,54</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.650.180,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$9.300.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:phoneticPr fontId="2" type="noConversion"/>
   <x:pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -67517,7 +67591,7 @@
   <documentManagement>
     <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
     <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-09-25T04:11:17+00:00</AtualizadoPeloTimerJobEm>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-09-27T04:01:02+00:00</AtualizadoPeloTimerJobEm>
   </documentManagement>
 </p:properties>
 </file>

--- a/DownloadTodosResultadosLoterias/downloads/SUPER_SETE.xlsx
+++ b/DownloadTodosResultadosLoterias/downloads/SUPER_SETE.xlsx
@@ -67591,7 +67591,7 @@
   <documentManagement>
     <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
     <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-09-27T04:01:02+00:00</AtualizadoPeloTimerJobEm>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-09-28T04:14:21+00:00</AtualizadoPeloTimerJobEm>
   </documentManagement>
 </p:properties>
 </file>

--- a/DownloadTodosResultadosLoterias/downloads/SUPER_SETE.xlsx
+++ b/DownloadTodosResultadosLoterias/downloads/SUPER_SETE.xlsx
@@ -67403,6 +67403,80 @@
         <x:v/>
       </x:c>
     </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>904</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>28/09/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$71.168,14</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.048,13</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1398</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$72,72</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12779</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$9.379.343,84</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.722.918,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$9.700.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:phoneticPr fontId="2" type="noConversion"/>
   <x:pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -67591,7 +67665,7 @@
   <documentManagement>
     <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
     <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-09-28T04:14:21+00:00</AtualizadoPeloTimerJobEm>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-09-29T04:12:24+00:00</AtualizadoPeloTimerJobEm>
   </documentManagement>
 </p:properties>
 </file>

--- a/DownloadTodosResultadosLoterias/downloads/SUPER_SETE.xlsx
+++ b/DownloadTodosResultadosLoterias/downloads/SUPER_SETE.xlsx
@@ -67477,6 +67477,80 @@
         <x:v/>
       </x:c>
     </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>905</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>30/09/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$32.972,88</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.095,44</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1249</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$75,42</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>11651</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$9.621.151,33</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.593.882,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$10.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:phoneticPr fontId="2" type="noConversion"/>
   <x:pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -67665,7 +67739,7 @@
   <documentManagement>
     <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
     <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-09-29T04:12:24+00:00</AtualizadoPeloTimerJobEm>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-10-01T04:13:26+00:00</AtualizadoPeloTimerJobEm>
   </documentManagement>
 </p:properties>
 </file>

--- a/DownloadTodosResultadosLoterias/downloads/SUPER_SETE.xlsx
+++ b/DownloadTodosResultadosLoterias/downloads/SUPER_SETE.xlsx
@@ -67551,6 +67551,154 @@
         <x:v/>
       </x:c>
     </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>906</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>02/10/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.218,21</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1459</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$75,14</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>14437</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$9.979.315,74</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.866.987,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$10.300.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>907</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>05/10/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$36.410,02</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.143,17</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1462</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$71,15</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>13379</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$10.246.327,81</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.767.066,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$10.500.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:phoneticPr fontId="2" type="noConversion"/>
   <x:pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -67739,7 +67887,7 @@
   <documentManagement>
     <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
     <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-10-01T04:13:26+00:00</AtualizadoPeloTimerJobEm>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-10-06T04:12:11+00:00</AtualizadoPeloTimerJobEm>
   </documentManagement>
 </p:properties>
 </file>

--- a/DownloadTodosResultadosLoterias/downloads/SUPER_SETE.xlsx
+++ b/DownloadTodosResultadosLoterias/downloads/SUPER_SETE.xlsx
@@ -67699,6 +67699,154 @@
         <x:v/>
       </x:c>
     </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>908</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>07/10/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$64.908,82</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.041,87</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1332</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$69,61</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>11606</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$10.484.331,58</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.570.713,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$10.800.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>909</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>09/10/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$64.117,94</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.144,96</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1184</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$77,36</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>11064</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$10.719.432,85</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.546.086,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$11.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:phoneticPr fontId="2" type="noConversion"/>
   <x:pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -67887,7 +68035,7 @@
   <documentManagement>
     <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
     <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-10-06T04:12:11+00:00</AtualizadoPeloTimerJobEm>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-10-11T04:12:43+00:00</AtualizadoPeloTimerJobEm>
   </documentManagement>
 </p:properties>
 </file>

--- a/DownloadTodosResultadosLoterias/downloads/SUPER_SETE.xlsx
+++ b/DownloadTodosResultadosLoterias/downloads/SUPER_SETE.xlsx
@@ -68035,7 +68035,7 @@
   <documentManagement>
     <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
     <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-10-11T04:12:43+00:00</AtualizadoPeloTimerJobEm>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-10-12T04:12:41+00:00</AtualizadoPeloTimerJobEm>
   </documentManagement>
 </p:properties>
 </file>
